--- a/artfynd/A 49799-2023 artfynd.xlsx
+++ b/artfynd/A 49799-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49799-2023 artfynd.xlsx
+++ b/artfynd/A 49799-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97474667</v>
+        <v>97474665</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598885.1353526916</v>
+        <v>598854</v>
       </c>
       <c r="R2" t="n">
-        <v>6845525.019817881</v>
+        <v>6845554</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97474665</v>
+        <v>97474669</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598853.9201174515</v>
+        <v>598894</v>
       </c>
       <c r="R3" t="n">
-        <v>6845553.522378841</v>
+        <v>6845560</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97474666</v>
+        <v>97474663</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598826.6539618582</v>
+        <v>598779</v>
       </c>
       <c r="R4" t="n">
-        <v>6845560.325276813</v>
+        <v>6845575</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97474669</v>
+        <v>97474667</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598893.6168276685</v>
+        <v>598885</v>
       </c>
       <c r="R5" t="n">
-        <v>6845560.3551532</v>
+        <v>6845525</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97474672</v>
+        <v>97474668</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598913.5419449221</v>
+        <v>598894</v>
       </c>
       <c r="R6" t="n">
-        <v>6845511.611179624</v>
+        <v>6845560</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97474668</v>
+        <v>97474666</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598893.6168276685</v>
+        <v>598827</v>
       </c>
       <c r="R7" t="n">
-        <v>6845560.3551532</v>
+        <v>6845561</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97474672</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Joseberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598913</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6845511</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
